--- a/upload/baselegal_creditopresumido.xlsx
+++ b/upload/baselegal_creditopresumido.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
   <si>
     <t>Base normativa para a concessão de regimes especiais com o tratamento tributário de Crédito Presumido</t>
   </si>
@@ -457,7 +457,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -595,17 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -687,19 +676,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -832,8 +808,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -843,125 +900,38 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1247,755 +1217,861 @@
   <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.42578125" style="43" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="43" customWidth="1"/>
-    <col min="4" max="4" width="33.140625" style="43" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.42578125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="3">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="11"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="D3" s="34"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>34</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="14"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="D4" s="36"/>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>35</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="16"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="D5" s="25"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>63</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="16"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="D6" s="25"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>69</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="16"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="D7" s="25"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>84</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="16"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="D8" s="25"/>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>98</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="17" t="s">
+      <c r="D9" s="27"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
         <v>104</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="16"/>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="D11" s="25"/>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
         <v>105</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="15" t="s">
+      <c r="B12" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="16"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="D12" s="25"/>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
         <v>106</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="15" t="s">
+      <c r="B13" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="16"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="D13" s="25"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
         <v>110</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="15" t="s">
+      <c r="B14" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="16"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="D14" s="25"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
         <v>117</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="15" t="s">
+      <c r="B15" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="16"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="D15" s="25"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
         <v>118</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="16"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="D16" s="25"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
         <v>120</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="16"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
         <v>123</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="16"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+      <c r="D18" s="25"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
         <v>124</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="15" t="s">
+      <c r="B19" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="16"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="D19" s="25"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
         <v>127</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="15" t="s">
+      <c r="B20" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="16"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="D20" s="25"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
         <v>128</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="15" t="s">
+      <c r="B21" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="16"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="D21" s="25"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
         <v>129</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="15" t="s">
+      <c r="B22" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="16"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="D22" s="25"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
         <v>130</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="15" t="s">
+      <c r="B23" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="16"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+      <c r="D23" s="25"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
         <v>132</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="15" t="s">
+      <c r="B24" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="16"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+      <c r="D24" s="25"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
         <v>139</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="15" t="s">
+      <c r="B25" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="16"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+      <c r="D25" s="25"/>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
         <v>140</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="15" t="s">
+      <c r="B26" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="16"/>
+      <c r="D26" s="25"/>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+      <c r="A27" s="3">
         <v>158</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20" t="s">
+      <c r="B27" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
+      <c r="A28" s="3">
         <v>187</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="24"/>
+      <c r="D28" s="21"/>
     </row>
     <row r="29" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+      <c r="A29" s="3">
         <v>185</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="21"/>
+      <c r="D29" s="23"/>
     </row>
     <row r="30" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="26" t="s">
+      <c r="A30" s="3"/>
+      <c r="B30" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="28"/>
+      <c r="D30" s="15"/>
     </row>
     <row r="31" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="29" t="s">
+      <c r="A31" s="3"/>
+      <c r="B31" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="31"/>
+      <c r="D31" s="17"/>
     </row>
     <row r="32" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="26" t="s">
+      <c r="A32" s="3"/>
+      <c r="B32" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D32" s="28"/>
+      <c r="D32" s="15"/>
     </row>
     <row r="33" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="29" t="s">
+      <c r="A33" s="3"/>
+      <c r="B33" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="30" t="s">
+      <c r="C33" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="31"/>
+      <c r="D33" s="17"/>
     </row>
     <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="26" t="s">
+      <c r="A34" s="3"/>
+      <c r="B34" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="28"/>
+      <c r="D34" s="15"/>
     </row>
     <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="29" t="s">
+      <c r="A35" s="3"/>
+      <c r="B35" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D35" s="31"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="26" t="s">
+      <c r="A36" s="3"/>
+      <c r="B36" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="33"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="34" t="s">
+      <c r="D36" s="19"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
+    <row r="38" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
         <v>327</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="36" t="s">
+      <c r="B38" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D38" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
+    <row r="39" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
         <v>329</v>
       </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="36" t="s">
+      <c r="B39" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
+    <row r="40" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
         <v>330</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="36" t="s">
+      <c r="B40" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="37" t="s">
+      <c r="D40" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
+    <row r="41" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
         <v>331</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="36" t="s">
+      <c r="B41" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="D41" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
+    <row r="42" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
         <v>337</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="36" t="s">
+      <c r="B42" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="37" t="s">
+      <c r="D42" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8">
+    <row r="43" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
         <v>340</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="36" t="s">
+      <c r="B43" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D43" s="37" t="s">
+      <c r="D43" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8">
+    <row r="44" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
         <v>343</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="36" t="s">
+      <c r="B44" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D44" s="37" t="s">
+      <c r="D44" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
+    <row r="45" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
         <v>355</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="36" t="s">
+      <c r="B45" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D45" s="37" t="s">
+      <c r="D45" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8">
+    <row r="46" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
         <v>356</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="36" t="s">
+      <c r="B46" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D46" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8">
+    <row r="47" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
         <v>358</v>
       </c>
-      <c r="B47" s="12"/>
-      <c r="C47" s="36" t="s">
+      <c r="B47" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D47" s="37" t="s">
+      <c r="D47" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
+    <row r="48" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
         <v>361</v>
       </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="36" t="s">
+      <c r="B48" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D48" s="37" t="s">
+      <c r="D48" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
+    <row r="49" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
         <v>362</v>
       </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="36" t="s">
+      <c r="B49" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="D49" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="8">
+    <row r="50" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
         <v>364</v>
       </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="36" t="s">
+      <c r="B50" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="37" t="s">
+      <c r="D50" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
+    <row r="51" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
         <v>365</v>
       </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="36" t="s">
+      <c r="B51" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="37" t="s">
+      <c r="D51" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="38" t="s">
+    <row r="52" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3"/>
+      <c r="B52" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="37" t="s">
+      <c r="D52" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8">
+    <row r="53" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
         <v>369</v>
       </c>
-      <c r="B53" s="12"/>
-      <c r="C53" s="36" t="s">
+      <c r="B53" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D53" s="37" t="s">
+      <c r="D53" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="38" t="s">
+    <row r="54" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3"/>
+      <c r="B54" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D54" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="8">
+    <row r="55" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
         <v>371</v>
       </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="38" t="s">
+      <c r="B55" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D55" s="37" t="s">
+      <c r="D55" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="8">
+    <row r="56" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
         <v>372</v>
       </c>
-      <c r="B56" s="12"/>
-      <c r="C56" s="36" t="s">
+      <c r="B56" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D56" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="8">
+    <row r="57" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
         <v>549</v>
       </c>
-      <c r="B57" s="12"/>
-      <c r="C57" s="36" t="s">
+      <c r="B57" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D57" s="37" t="s">
+      <c r="D57" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="8">
+    <row r="58" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
         <v>559</v>
       </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="36" t="s">
+      <c r="B58" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D58" s="37" t="s">
+      <c r="D58" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="8">
+    <row r="59" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
         <v>568</v>
       </c>
-      <c r="B59" s="12"/>
-      <c r="C59" s="38" t="s">
+      <c r="B59" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D59" s="37" t="s">
+      <c r="D59" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
+    <row r="60" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
         <v>577</v>
       </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="38" t="s">
+      <c r="B60" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D60" s="37" t="s">
+      <c r="D60" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="8">
+    <row r="61" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3">
         <v>578</v>
       </c>
-      <c r="B61" s="12"/>
-      <c r="C61" s="38" t="s">
+      <c r="B61" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D61" s="37" t="s">
+      <c r="D61" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="8">
+    <row r="62" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
         <v>579</v>
       </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="38" t="s">
+      <c r="B62" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D62" s="37" t="s">
+      <c r="D62" s="7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="8">
+    <row r="63" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
         <v>586</v>
       </c>
-      <c r="B63" s="12"/>
-      <c r="C63" s="38" t="s">
+      <c r="B63" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D63" s="37" t="s">
+      <c r="D63" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="8">
+    <row r="64" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
         <v>608</v>
       </c>
-      <c r="B64" s="12"/>
-      <c r="C64" s="38" t="s">
+      <c r="B64" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D64" s="37" t="s">
+      <c r="D64" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="8"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="38" t="s">
+    <row r="65" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3"/>
+      <c r="B65" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D65" s="37" t="s">
+      <c r="D65" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="8"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="38" t="s">
+    <row r="66" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3"/>
+      <c r="B66" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D66" s="37" t="s">
+      <c r="D66" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="39"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="40" t="s">
+    <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9"/>
+      <c r="B67" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D67" s="41" t="s">
+      <c r="D67" s="11" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B37:B67"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
+  <mergeCells count="36">
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
@@ -2003,22 +2079,20 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="B3:B27"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D38" r:id="rId1" location="art31"/>
